--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -93,21 +93,6 @@
   </si>
   <si>
     <t>字段变体</t>
-  </si>
-  <si>
-    <t>MonsterSpawnWaves</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>Num</t>
   </si>
 </sst>
 </file>
@@ -1162,30 +1147,18 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="L4" s="3"/>
       <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="J5" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="L5" s="3"/>
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:16">
